--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -1695,7 +1695,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1784,10 +1784,20 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1809,17 +1819,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2065,30 +2071,30 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="E1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="50" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="54"/>
     </row>
     <row r="3" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="57"/>
     </row>
     <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="5" t="s">
@@ -2097,14 +2103,14 @@
       <c r="B4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="65" t="s">
         <v>424</v>
       </c>
-      <c r="D4" s="62" t="s">
+      <c r="D4" s="48" t="s">
         <v>424</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="63" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="49" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2115,10 +2121,16 @@
       <c r="B5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
+      <c r="C5" s="65" t="s">
+        <v>424</v>
+      </c>
+      <c r="D5" s="66" t="s">
+        <v>424</v>
+      </c>
+      <c r="E5" s="46"/>
+      <c r="F5" s="67" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="12.75">
       <c r="A6" s="5" t="s">
@@ -2199,14 +2211,14 @@
       <c r="B12" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="51" t="s">
         <v>424</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="D12" s="48" t="s">
         <v>424</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="63" t="s">
+      <c r="E12" s="46"/>
+      <c r="F12" s="49" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2235,22 +2247,22 @@
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="12.75">
-      <c r="A15" s="48" t="s">
+      <c r="A15" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="49"/>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="50"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="54"/>
     </row>
     <row r="16" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="53"/>
+      <c r="A16" s="55"/>
+      <c r="B16" s="56"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="57"/>
     </row>
     <row r="17" spans="1:6" ht="12.75">
       <c r="A17" s="25" t="s">
@@ -2585,22 +2597,22 @@
       <c r="F46" s="10"/>
     </row>
     <row r="47" spans="1:6" ht="12.75">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="49"/>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="50"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
     </row>
     <row r="48" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A48" s="51"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="53"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="57"/>
     </row>
     <row r="49" spans="1:6" ht="12.75">
       <c r="A49" s="15" t="s">
@@ -3683,22 +3695,22 @@
       <c r="F138" s="10"/>
     </row>
     <row r="139" spans="1:6" ht="12.75">
-      <c r="A139" s="55" t="s">
+      <c r="A139" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="B139" s="56"/>
-      <c r="C139" s="56"/>
-      <c r="D139" s="56"/>
-      <c r="E139" s="56"/>
-      <c r="F139" s="57"/>
+      <c r="B139" s="60"/>
+      <c r="C139" s="60"/>
+      <c r="D139" s="60"/>
+      <c r="E139" s="60"/>
+      <c r="F139" s="61"/>
     </row>
     <row r="140" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A140" s="58"/>
-      <c r="B140" s="59"/>
-      <c r="C140" s="59"/>
-      <c r="D140" s="59"/>
-      <c r="E140" s="59"/>
-      <c r="F140" s="60"/>
+      <c r="A140" s="62"/>
+      <c r="B140" s="63"/>
+      <c r="C140" s="63"/>
+      <c r="D140" s="63"/>
+      <c r="E140" s="63"/>
+      <c r="F140" s="64"/>
     </row>
     <row r="141" spans="1:6" ht="12.75">
       <c r="A141" s="45" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$225</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -2139,10 +2142,16 @@
       <c r="B6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
+      <c r="C6" s="65" t="s">
+        <v>424</v>
+      </c>
+      <c r="D6" s="66" t="s">
+        <v>424</v>
+      </c>
+      <c r="E6" s="46"/>
+      <c r="F6" s="67" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="12.75">
       <c r="A7" s="5" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -2160,10 +2160,16 @@
       <c r="B7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
+      <c r="C7" s="65" t="s">
+        <v>424</v>
+      </c>
+      <c r="D7" s="66" t="s">
+        <v>424</v>
+      </c>
+      <c r="E7" s="46"/>
+      <c r="F7" s="67" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="12.75">
       <c r="A8" s="5" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -1803,6 +1803,15 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1822,15 +1831,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2082,22 +2082,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="54"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
     </row>
     <row r="3" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A3" s="55"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="57"/>
+      <c r="A3" s="58"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="60"/>
     </row>
     <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="5" t="s">
@@ -2106,7 +2106,7 @@
       <c r="B4" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="52" t="s">
         <v>424</v>
       </c>
       <c r="D4" s="48" t="s">
@@ -2124,14 +2124,14 @@
       <c r="B5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="65" t="s">
+      <c r="C5" s="52" t="s">
         <v>424</v>
       </c>
-      <c r="D5" s="66" t="s">
+      <c r="D5" s="53" t="s">
         <v>424</v>
       </c>
       <c r="E5" s="46"/>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="54" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2142,14 +2142,14 @@
       <c r="B6" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="52" t="s">
         <v>424</v>
       </c>
-      <c r="D6" s="66" t="s">
+      <c r="D6" s="53" t="s">
         <v>424</v>
       </c>
       <c r="E6" s="46"/>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="54" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2160,14 +2160,14 @@
       <c r="B7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="52" t="s">
         <v>424</v>
       </c>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="53" t="s">
         <v>424</v>
       </c>
       <c r="E7" s="46"/>
-      <c r="F7" s="67" t="s">
+      <c r="F7" s="54" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2178,10 +2178,16 @@
       <c r="B8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
+      <c r="C8" s="52" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="53" t="s">
+        <v>424</v>
+      </c>
+      <c r="E8" s="46"/>
+      <c r="F8" s="54" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
       <c r="A9" s="5" t="s">
@@ -2262,22 +2268,22 @@
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="12.75">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="55" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="54"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="57"/>
     </row>
     <row r="16" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A16" s="55"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="57"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="60"/>
     </row>
     <row r="17" spans="1:6" ht="12.75">
       <c r="A17" s="25" t="s">
@@ -2612,22 +2618,22 @@
       <c r="F46" s="10"/>
     </row>
     <row r="47" spans="1:6" ht="12.75">
-      <c r="A47" s="58" t="s">
+      <c r="A47" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="54"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="57"/>
     </row>
     <row r="48" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A48" s="55"/>
-      <c r="B48" s="56"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="57"/>
+      <c r="A48" s="58"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="60"/>
     </row>
     <row r="49" spans="1:6" ht="12.75">
       <c r="A49" s="15" t="s">
@@ -3710,22 +3716,22 @@
       <c r="F138" s="10"/>
     </row>
     <row r="139" spans="1:6" ht="12.75">
-      <c r="A139" s="59" t="s">
+      <c r="A139" s="62" t="s">
         <v>120</v>
       </c>
-      <c r="B139" s="60"/>
-      <c r="C139" s="60"/>
-      <c r="D139" s="60"/>
-      <c r="E139" s="60"/>
-      <c r="F139" s="61"/>
+      <c r="B139" s="63"/>
+      <c r="C139" s="63"/>
+      <c r="D139" s="63"/>
+      <c r="E139" s="63"/>
+      <c r="F139" s="64"/>
     </row>
     <row r="140" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A140" s="62"/>
-      <c r="B140" s="63"/>
-      <c r="C140" s="63"/>
-      <c r="D140" s="63"/>
-      <c r="E140" s="63"/>
-      <c r="F140" s="64"/>
+      <c r="A140" s="65"/>
+      <c r="B140" s="66"/>
+      <c r="C140" s="66"/>
+      <c r="D140" s="66"/>
+      <c r="E140" s="66"/>
+      <c r="F140" s="67"/>
     </row>
     <row r="141" spans="1:6" ht="12.75">
       <c r="A141" s="45" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -18,6 +18,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$225</definedName>
   </definedNames>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -1699,7 +1699,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1832,6 +1832,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2197,10 +2209,16 @@
       <c r="B9" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
+      <c r="C9" s="68" t="s">
+        <v>424</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>424</v>
+      </c>
+      <c r="E9" s="70"/>
+      <c r="F9" s="71" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
       <c r="A10" s="5" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -1699,7 +1699,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1842,6 +1842,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2227,10 +2233,16 @@
       <c r="B10" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="10"/>
+      <c r="C10" s="72" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" s="73" t="s">
+        <v>424</v>
+      </c>
+      <c r="E10" s="70"/>
+      <c r="F10" s="71" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
       <c r="A11" s="5" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -2251,10 +2251,16 @@
       <c r="B11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10"/>
+      <c r="C11" s="68" t="s">
+        <v>424</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>424</v>
+      </c>
+      <c r="E11" s="70"/>
+      <c r="F11" s="71" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
       <c r="A12" s="5" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -18,12 +18,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$F$225</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -1813,6 +1812,24 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1832,24 +1849,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2101,22 +2100,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.75">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="63"/>
     </row>
     <row r="3" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="60"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="66"/>
     </row>
     <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="5" t="s">
@@ -2215,14 +2214,14 @@
       <c r="B9" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="68" t="s">
+      <c r="C9" s="55" t="s">
         <v>424</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="56" t="s">
         <v>424</v>
       </c>
-      <c r="E9" s="70"/>
-      <c r="F9" s="71" t="s">
+      <c r="E9" s="57"/>
+      <c r="F9" s="58" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2233,14 +2232,14 @@
       <c r="B10" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="72" t="s">
+      <c r="C10" s="59" t="s">
         <v>424</v>
       </c>
-      <c r="D10" s="73" t="s">
+      <c r="D10" s="60" t="s">
         <v>424</v>
       </c>
-      <c r="E10" s="70"/>
-      <c r="F10" s="71" t="s">
+      <c r="E10" s="57"/>
+      <c r="F10" s="58" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2251,14 +2250,14 @@
       <c r="B11" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="68" t="s">
+      <c r="C11" s="55" t="s">
         <v>424</v>
       </c>
-      <c r="D11" s="69" t="s">
+      <c r="D11" s="56" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="71" t="s">
+      <c r="E11" s="57"/>
+      <c r="F11" s="58" t="s">
         <v>424</v>
       </c>
     </row>
@@ -2287,10 +2286,16 @@
       <c r="B13" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10"/>
+      <c r="C13" s="55" t="s">
+        <v>424</v>
+      </c>
+      <c r="D13" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="E13" s="57"/>
+      <c r="F13" s="58" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="13.5" thickBot="1">
       <c r="A14" s="5" t="s">
@@ -2305,22 +2310,22 @@
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" ht="12.75">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="57"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="63"/>
     </row>
     <row r="16" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A16" s="58"/>
-      <c r="B16" s="59"/>
-      <c r="C16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="F16" s="60"/>
+      <c r="A16" s="64"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66"/>
     </row>
     <row r="17" spans="1:6" ht="12.75">
       <c r="A17" s="25" t="s">
@@ -2655,22 +2660,22 @@
       <c r="F46" s="10"/>
     </row>
     <row r="47" spans="1:6" ht="12.75">
-      <c r="A47" s="61" t="s">
+      <c r="A47" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="B47" s="56"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="57"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="63"/>
     </row>
     <row r="48" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A48" s="58"/>
-      <c r="B48" s="59"/>
-      <c r="C48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="F48" s="60"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="66"/>
     </row>
     <row r="49" spans="1:6" ht="12.75">
       <c r="A49" s="15" t="s">
@@ -3753,22 +3758,22 @@
       <c r="F138" s="10"/>
     </row>
     <row r="139" spans="1:6" ht="12.75">
-      <c r="A139" s="62" t="s">
+      <c r="A139" s="68" t="s">
         <v>120</v>
       </c>
-      <c r="B139" s="63"/>
-      <c r="C139" s="63"/>
-      <c r="D139" s="63"/>
-      <c r="E139" s="63"/>
-      <c r="F139" s="64"/>
+      <c r="B139" s="69"/>
+      <c r="C139" s="69"/>
+      <c r="D139" s="69"/>
+      <c r="E139" s="69"/>
+      <c r="F139" s="70"/>
     </row>
     <row r="140" spans="1:6" ht="13.5" thickBot="1">
-      <c r="A140" s="65"/>
-      <c r="B140" s="66"/>
-      <c r="C140" s="66"/>
-      <c r="D140" s="66"/>
-      <c r="E140" s="66"/>
-      <c r="F140" s="67"/>
+      <c r="A140" s="71"/>
+      <c r="B140" s="72"/>
+      <c r="C140" s="72"/>
+      <c r="D140" s="72"/>
+      <c r="E140" s="72"/>
+      <c r="F140" s="73"/>
     </row>
     <row r="141" spans="1:6" ht="12.75">
       <c r="A141" s="45" t="s">

--- a/SpectrobesSFM checklist.xlsx
+++ b/SpectrobesSFM checklist.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="426">
   <si>
     <t>ID</t>
   </si>
@@ -2286,7 +2286,7 @@
       <c r="B13" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="59" t="s">
         <v>424</v>
       </c>
       <c r="D13" s="56" t="s">
@@ -2304,10 +2304,16 @@
       <c r="B14" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10"/>
+      <c r="C14" s="55" t="s">
+        <v>424</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>424</v>
+      </c>
+      <c r="E14" s="57"/>
+      <c r="F14" s="58" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="12.75">
       <c r="A15" s="61" t="s">
